--- a/erp-server/erp-server-scm/src/main/resources/excel/assetPurchaseOrderTemplate.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/assetPurchaseOrderTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <r>
       <rPr>
@@ -208,13 +208,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -226,6 +219,21 @@
         <scheme val="minor"/>
       </rPr>
       <t>是否加急</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否赠品</t>
     </r>
   </si>
   <si>
@@ -1424,7 +1432,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.6333333333333" customWidth="1"/>
@@ -1442,10 +1450,10 @@
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="12.6333333333333" customWidth="1"/>
     <col min="15" max="16" width="14.275" customWidth="1"/>
-    <col min="17" max="17" width="13.1833333333333" customWidth="1"/>
+    <col min="17" max="18" width="13.1833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" spans="1:18">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1494,13 +1502,16 @@
       <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576 Q2:Q1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
